--- a/assets/Ra_Soat_Thiet_Bi_CNTT.xlsx
+++ b/assets/Ra_Soat_Thiet_Bi_CNTT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\Phần mềm lấy dữ liệu doanh thu BCCP\device-inventory-web\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD032AF-2F66-41A8-89E7-42B29DCA3644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94900D46-BD9B-4B29-96FC-80DFE65E9050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="827" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="827" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Hidden" sheetId="1" state="hidden" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. Danh Mục CCDC Tổng'!$A$4:$D$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Máy Tính'!$A$4:$AF$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Máy Tính'!$A$4:$AB$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4A. Máy In Laser'!$A$4:$W$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4B. Máy In Nhiệt'!$A$4:$W$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'4C. Máy Photocopy'!$A$4:$AA$54</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="202">
   <si>
     <t>3. Máy Tính</t>
   </si>
@@ -5663,7 +5663,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AF54"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5672,35 +5672,33 @@
     <col min="8" max="8" width="28" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="41" customWidth="1"/>
-    <col min="13" max="13" width="37" customWidth="1"/>
-    <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="15" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="22" width="15" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
-    <col min="29" max="29" width="35" customWidth="1"/>
-    <col min="30" max="30" width="16" customWidth="1"/>
-    <col min="31" max="31" width="33" customWidth="1"/>
-    <col min="32" max="32" width="15" customWidth="1"/>
+    <col min="11" max="11" width="41" customWidth="1"/>
+    <col min="12" max="12" width="37" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="22" width="15" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="35" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="33" customWidth="1"/>
+    <col min="28" max="28" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>98</v>
       </c>
@@ -5732,73 +5730,61 @@
         <v>143</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O4" s="13" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="V4" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W4" s="13" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="X4" s="13" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="Y4" s="13" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AA4" s="13" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD4" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF4" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>1</v>
       </c>
@@ -5812,29 +5798,25 @@
       <c r="I5" s="14"/>
       <c r="J5" s="3"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="14"/>
-      <c r="S5" s="3"/>
+      <c r="S5" s="14"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="14"/>
+      <c r="U5" s="3"/>
       <c r="V5" s="14"/>
-      <c r="W5" s="3"/>
+      <c r="W5" s="14"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-    </row>
-    <row r="6" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>2</v>
       </c>
@@ -5848,29 +5830,25 @@
       <c r="I6" s="15"/>
       <c r="J6" s="16"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="L6" s="16"/>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="15"/>
-      <c r="S6" s="16"/>
+      <c r="S6" s="15"/>
       <c r="T6" s="16"/>
-      <c r="U6" s="15"/>
+      <c r="U6" s="16"/>
       <c r="V6" s="15"/>
-      <c r="W6" s="16"/>
+      <c r="W6" s="15"/>
       <c r="X6" s="16"/>
       <c r="Y6" s="16"/>
       <c r="Z6" s="15"/>
-      <c r="AA6" s="15"/>
+      <c r="AA6" s="16"/>
       <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="15"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-    </row>
-    <row r="7" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>3</v>
       </c>
@@ -5884,29 +5862,25 @@
       <c r="I7" s="14"/>
       <c r="J7" s="3"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="14"/>
-      <c r="S7" s="3"/>
+      <c r="S7" s="14"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="14"/>
+      <c r="U7" s="3"/>
       <c r="V7" s="14"/>
-      <c r="W7" s="3"/>
+      <c r="W7" s="14"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
-    </row>
-    <row r="8" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>4</v>
       </c>
@@ -5920,29 +5894,25 @@
       <c r="I8" s="15"/>
       <c r="J8" s="16"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="15"/>
-      <c r="S8" s="16"/>
+      <c r="S8" s="15"/>
       <c r="T8" s="16"/>
-      <c r="U8" s="15"/>
+      <c r="U8" s="16"/>
       <c r="V8" s="15"/>
-      <c r="W8" s="16"/>
+      <c r="W8" s="15"/>
       <c r="X8" s="16"/>
       <c r="Y8" s="16"/>
       <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
+      <c r="AA8" s="16"/>
       <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-    </row>
-    <row r="9" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>5</v>
       </c>
@@ -5956,29 +5926,25 @@
       <c r="I9" s="14"/>
       <c r="J9" s="3"/>
       <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="14"/>
-      <c r="S9" s="3"/>
+      <c r="S9" s="14"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="14"/>
+      <c r="U9" s="3"/>
       <c r="V9" s="14"/>
-      <c r="W9" s="3"/>
+      <c r="W9" s="14"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-    </row>
-    <row r="10" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>6</v>
       </c>
@@ -5992,29 +5958,25 @@
       <c r="I10" s="15"/>
       <c r="J10" s="16"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
+      <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="15"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="15"/>
       <c r="T10" s="16"/>
-      <c r="U10" s="15"/>
+      <c r="U10" s="16"/>
       <c r="V10" s="15"/>
-      <c r="W10" s="16"/>
+      <c r="W10" s="15"/>
       <c r="X10" s="16"/>
       <c r="Y10" s="16"/>
       <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
+      <c r="AA10" s="16"/>
       <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-    </row>
-    <row r="11" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>7</v>
       </c>
@@ -6028,29 +5990,25 @@
       <c r="I11" s="14"/>
       <c r="J11" s="3"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="14"/>
-      <c r="S11" s="3"/>
+      <c r="S11" s="14"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="14"/>
+      <c r="U11" s="3"/>
       <c r="V11" s="14"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="14"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15">
         <v>8</v>
       </c>
@@ -6064,29 +6022,25 @@
       <c r="I12" s="15"/>
       <c r="J12" s="16"/>
       <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
+      <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
       <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="15"/>
-      <c r="S12" s="16"/>
+      <c r="S12" s="15"/>
       <c r="T12" s="16"/>
-      <c r="U12" s="15"/>
+      <c r="U12" s="16"/>
       <c r="V12" s="15"/>
-      <c r="W12" s="16"/>
+      <c r="W12" s="15"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
+      <c r="AA12" s="16"/>
       <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-    </row>
-    <row r="13" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>9</v>
       </c>
@@ -6100,29 +6054,25 @@
       <c r="I13" s="14"/>
       <c r="J13" s="3"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="14"/>
-      <c r="S13" s="3"/>
+      <c r="S13" s="14"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="14"/>
+      <c r="U13" s="3"/>
       <c r="V13" s="14"/>
-      <c r="W13" s="3"/>
+      <c r="W13" s="14"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-    </row>
-    <row r="14" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15">
         <v>10</v>
       </c>
@@ -6136,29 +6086,25 @@
       <c r="I14" s="15"/>
       <c r="J14" s="16"/>
       <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+      <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="15"/>
-      <c r="S14" s="16"/>
+      <c r="S14" s="15"/>
       <c r="T14" s="16"/>
-      <c r="U14" s="15"/>
+      <c r="U14" s="16"/>
       <c r="V14" s="15"/>
-      <c r="W14" s="16"/>
+      <c r="W14" s="15"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
+      <c r="AA14" s="16"/>
       <c r="AB14" s="16"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="15"/>
-      <c r="AE14" s="16"/>
-      <c r="AF14" s="16"/>
-    </row>
-    <row r="15" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>11</v>
       </c>
@@ -6172,29 +6118,25 @@
       <c r="I15" s="14"/>
       <c r="J15" s="3"/>
       <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="14"/>
-      <c r="S15" s="3"/>
+      <c r="S15" s="14"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="14"/>
+      <c r="U15" s="3"/>
       <c r="V15" s="14"/>
-      <c r="W15" s="3"/>
+      <c r="W15" s="14"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-    </row>
-    <row r="16" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15">
         <v>12</v>
       </c>
@@ -6208,29 +6150,25 @@
       <c r="I16" s="15"/>
       <c r="J16" s="16"/>
       <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
+      <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="15"/>
-      <c r="S16" s="16"/>
+      <c r="S16" s="15"/>
       <c r="T16" s="16"/>
-      <c r="U16" s="15"/>
+      <c r="U16" s="16"/>
       <c r="V16" s="15"/>
-      <c r="W16" s="16"/>
+      <c r="W16" s="15"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
       <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
+      <c r="AA16" s="16"/>
       <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="16"/>
-      <c r="AF16" s="16"/>
-    </row>
-    <row r="17" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>13</v>
       </c>
@@ -6244,29 +6182,25 @@
       <c r="I17" s="14"/>
       <c r="J17" s="3"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="14"/>
-      <c r="S17" s="3"/>
+      <c r="S17" s="14"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="14"/>
+      <c r="U17" s="3"/>
       <c r="V17" s="14"/>
-      <c r="W17" s="3"/>
+      <c r="W17" s="14"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-    </row>
-    <row r="18" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15">
         <v>14</v>
       </c>
@@ -6280,29 +6214,25 @@
       <c r="I18" s="15"/>
       <c r="J18" s="16"/>
       <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
+      <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="15"/>
-      <c r="S18" s="16"/>
+      <c r="S18" s="15"/>
       <c r="T18" s="16"/>
-      <c r="U18" s="15"/>
+      <c r="U18" s="16"/>
       <c r="V18" s="15"/>
-      <c r="W18" s="16"/>
+      <c r="W18" s="15"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="16"/>
       <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
+      <c r="AA18" s="16"/>
       <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="16"/>
-      <c r="AF18" s="16"/>
-    </row>
-    <row r="19" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>15</v>
       </c>
@@ -6316,29 +6246,25 @@
       <c r="I19" s="14"/>
       <c r="J19" s="3"/>
       <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="14"/>
-      <c r="S19" s="3"/>
+      <c r="S19" s="14"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="14"/>
+      <c r="U19" s="3"/>
       <c r="V19" s="14"/>
-      <c r="W19" s="3"/>
+      <c r="W19" s="14"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>16</v>
       </c>
@@ -6352,29 +6278,25 @@
       <c r="I20" s="15"/>
       <c r="J20" s="16"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
+      <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="15"/>
-      <c r="S20" s="16"/>
+      <c r="S20" s="15"/>
       <c r="T20" s="16"/>
-      <c r="U20" s="15"/>
+      <c r="U20" s="16"/>
       <c r="V20" s="15"/>
-      <c r="W20" s="16"/>
+      <c r="W20" s="15"/>
       <c r="X20" s="16"/>
       <c r="Y20" s="16"/>
       <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
+      <c r="AA20" s="16"/>
       <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="15"/>
-      <c r="AE20" s="16"/>
-      <c r="AF20" s="16"/>
-    </row>
-    <row r="21" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>17</v>
       </c>
@@ -6388,29 +6310,25 @@
       <c r="I21" s="14"/>
       <c r="J21" s="3"/>
       <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="14"/>
-      <c r="S21" s="3"/>
+      <c r="S21" s="14"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="14"/>
+      <c r="U21" s="3"/>
       <c r="V21" s="14"/>
-      <c r="W21" s="3"/>
+      <c r="W21" s="14"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-    </row>
-    <row r="22" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>18</v>
       </c>
@@ -6424,29 +6342,25 @@
       <c r="I22" s="15"/>
       <c r="J22" s="16"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
+      <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
       <c r="R22" s="15"/>
-      <c r="S22" s="16"/>
+      <c r="S22" s="15"/>
       <c r="T22" s="16"/>
-      <c r="U22" s="15"/>
+      <c r="U22" s="16"/>
       <c r="V22" s="15"/>
-      <c r="W22" s="16"/>
+      <c r="W22" s="15"/>
       <c r="X22" s="16"/>
       <c r="Y22" s="16"/>
       <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
+      <c r="AA22" s="16"/>
       <c r="AB22" s="16"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="16"/>
-      <c r="AF22" s="16"/>
-    </row>
-    <row r="23" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>19</v>
       </c>
@@ -6460,29 +6374,25 @@
       <c r="I23" s="14"/>
       <c r="J23" s="3"/>
       <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="14"/>
-      <c r="S23" s="3"/>
+      <c r="S23" s="14"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="14"/>
+      <c r="U23" s="3"/>
       <c r="V23" s="14"/>
-      <c r="W23" s="3"/>
+      <c r="W23" s="14"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
       <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="3"/>
-    </row>
-    <row r="24" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>20</v>
       </c>
@@ -6496,29 +6406,25 @@
       <c r="I24" s="15"/>
       <c r="J24" s="16"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="15"/>
-      <c r="S24" s="16"/>
+      <c r="S24" s="15"/>
       <c r="T24" s="16"/>
-      <c r="U24" s="15"/>
+      <c r="U24" s="16"/>
       <c r="V24" s="15"/>
-      <c r="W24" s="16"/>
+      <c r="W24" s="15"/>
       <c r="X24" s="16"/>
       <c r="Y24" s="16"/>
       <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
+      <c r="AA24" s="16"/>
       <c r="AB24" s="16"/>
-      <c r="AC24" s="16"/>
-      <c r="AD24" s="15"/>
-      <c r="AE24" s="16"/>
-      <c r="AF24" s="16"/>
-    </row>
-    <row r="25" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>21</v>
       </c>
@@ -6532,29 +6438,25 @@
       <c r="I25" s="14"/>
       <c r="J25" s="3"/>
       <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="14"/>
-      <c r="S25" s="3"/>
+      <c r="S25" s="14"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="14"/>
+      <c r="U25" s="3"/>
       <c r="V25" s="14"/>
-      <c r="W25" s="3"/>
+      <c r="W25" s="14"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-    </row>
-    <row r="26" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>22</v>
       </c>
@@ -6568,29 +6470,25 @@
       <c r="I26" s="15"/>
       <c r="J26" s="16"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
+      <c r="L26" s="16"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
       <c r="P26" s="16"/>
       <c r="Q26" s="16"/>
       <c r="R26" s="15"/>
-      <c r="S26" s="16"/>
+      <c r="S26" s="15"/>
       <c r="T26" s="16"/>
-      <c r="U26" s="15"/>
+      <c r="U26" s="16"/>
       <c r="V26" s="15"/>
-      <c r="W26" s="16"/>
+      <c r="W26" s="15"/>
       <c r="X26" s="16"/>
       <c r="Y26" s="16"/>
       <c r="Z26" s="15"/>
-      <c r="AA26" s="15"/>
+      <c r="AA26" s="16"/>
       <c r="AB26" s="16"/>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="16"/>
-      <c r="AF26" s="16"/>
-    </row>
-    <row r="27" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>23</v>
       </c>
@@ -6604,29 +6502,25 @@
       <c r="I27" s="14"/>
       <c r="J27" s="3"/>
       <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="14"/>
-      <c r="S27" s="3"/>
+      <c r="S27" s="14"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="14"/>
+      <c r="U27" s="3"/>
       <c r="V27" s="14"/>
-      <c r="W27" s="3"/>
+      <c r="W27" s="14"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="14"/>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="3"/>
-    </row>
-    <row r="28" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>24</v>
       </c>
@@ -6640,29 +6534,25 @@
       <c r="I28" s="15"/>
       <c r="J28" s="16"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
+      <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
       <c r="O28" s="16"/>
       <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
       <c r="R28" s="15"/>
-      <c r="S28" s="16"/>
+      <c r="S28" s="15"/>
       <c r="T28" s="16"/>
-      <c r="U28" s="15"/>
+      <c r="U28" s="16"/>
       <c r="V28" s="15"/>
-      <c r="W28" s="16"/>
+      <c r="W28" s="15"/>
       <c r="X28" s="16"/>
       <c r="Y28" s="16"/>
       <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
+      <c r="AA28" s="16"/>
       <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-    </row>
-    <row r="29" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>25</v>
       </c>
@@ -6676,29 +6566,25 @@
       <c r="I29" s="14"/>
       <c r="J29" s="3"/>
       <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
+      <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="14"/>
-      <c r="S29" s="3"/>
+      <c r="S29" s="14"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="14"/>
+      <c r="U29" s="3"/>
       <c r="V29" s="14"/>
-      <c r="W29" s="3"/>
+      <c r="W29" s="14"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
-      <c r="AC29" s="3"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="3"/>
-      <c r="AF29" s="3"/>
-    </row>
-    <row r="30" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15">
         <v>26</v>
       </c>
@@ -6712,29 +6598,25 @@
       <c r="I30" s="15"/>
       <c r="J30" s="16"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
+      <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="15"/>
-      <c r="S30" s="16"/>
+      <c r="S30" s="15"/>
       <c r="T30" s="16"/>
-      <c r="U30" s="15"/>
+      <c r="U30" s="16"/>
       <c r="V30" s="15"/>
-      <c r="W30" s="16"/>
+      <c r="W30" s="15"/>
       <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
+      <c r="AA30" s="16"/>
       <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="15"/>
-      <c r="AE30" s="16"/>
-      <c r="AF30" s="16"/>
-    </row>
-    <row r="31" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
         <v>27</v>
       </c>
@@ -6748,29 +6630,25 @@
       <c r="I31" s="14"/>
       <c r="J31" s="3"/>
       <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="14"/>
-      <c r="S31" s="3"/>
+      <c r="S31" s="14"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="14"/>
+      <c r="U31" s="3"/>
       <c r="V31" s="14"/>
-      <c r="W31" s="3"/>
+      <c r="W31" s="14"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
-      <c r="AC31" s="3"/>
-      <c r="AD31" s="14"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="3"/>
-    </row>
-    <row r="32" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
         <v>28</v>
       </c>
@@ -6784,29 +6662,25 @@
       <c r="I32" s="15"/>
       <c r="J32" s="16"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
+      <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
       <c r="O32" s="16"/>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
       <c r="R32" s="15"/>
-      <c r="S32" s="16"/>
+      <c r="S32" s="15"/>
       <c r="T32" s="16"/>
-      <c r="U32" s="15"/>
+      <c r="U32" s="16"/>
       <c r="V32" s="15"/>
-      <c r="W32" s="16"/>
+      <c r="W32" s="15"/>
       <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
+      <c r="AA32" s="16"/>
       <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="15"/>
-      <c r="AE32" s="16"/>
-      <c r="AF32" s="16"/>
-    </row>
-    <row r="33" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
         <v>29</v>
       </c>
@@ -6820,29 +6694,25 @@
       <c r="I33" s="14"/>
       <c r="J33" s="3"/>
       <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="14"/>
-      <c r="S33" s="3"/>
+      <c r="S33" s="14"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="14"/>
+      <c r="U33" s="3"/>
       <c r="V33" s="14"/>
-      <c r="W33" s="3"/>
+      <c r="W33" s="14"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
-    </row>
-    <row r="34" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15">
         <v>30</v>
       </c>
@@ -6856,29 +6726,25 @@
       <c r="I34" s="15"/>
       <c r="J34" s="16"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
+      <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
       <c r="R34" s="15"/>
-      <c r="S34" s="16"/>
+      <c r="S34" s="15"/>
       <c r="T34" s="16"/>
-      <c r="U34" s="15"/>
+      <c r="U34" s="16"/>
       <c r="V34" s="15"/>
-      <c r="W34" s="16"/>
+      <c r="W34" s="15"/>
       <c r="X34" s="16"/>
       <c r="Y34" s="16"/>
       <c r="Z34" s="15"/>
-      <c r="AA34" s="15"/>
+      <c r="AA34" s="16"/>
       <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="15"/>
-      <c r="AE34" s="16"/>
-      <c r="AF34" s="16"/>
-    </row>
-    <row r="35" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>31</v>
       </c>
@@ -6892,29 +6758,25 @@
       <c r="I35" s="14"/>
       <c r="J35" s="3"/>
       <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="14"/>
-      <c r="S35" s="3"/>
+      <c r="S35" s="14"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="14"/>
+      <c r="U35" s="3"/>
       <c r="V35" s="14"/>
-      <c r="W35" s="3"/>
+      <c r="W35" s="14"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
-      <c r="AC35" s="3"/>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="3"/>
-      <c r="AF35" s="3"/>
-    </row>
-    <row r="36" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <v>32</v>
       </c>
@@ -6928,29 +6790,25 @@
       <c r="I36" s="15"/>
       <c r="J36" s="16"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
+      <c r="L36" s="16"/>
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
       <c r="O36" s="16"/>
       <c r="P36" s="16"/>
       <c r="Q36" s="16"/>
       <c r="R36" s="15"/>
-      <c r="S36" s="16"/>
+      <c r="S36" s="15"/>
       <c r="T36" s="16"/>
-      <c r="U36" s="15"/>
+      <c r="U36" s="16"/>
       <c r="V36" s="15"/>
-      <c r="W36" s="16"/>
+      <c r="W36" s="15"/>
       <c r="X36" s="16"/>
       <c r="Y36" s="16"/>
       <c r="Z36" s="15"/>
-      <c r="AA36" s="15"/>
+      <c r="AA36" s="16"/>
       <c r="AB36" s="16"/>
-      <c r="AC36" s="16"/>
-      <c r="AD36" s="15"/>
-      <c r="AE36" s="16"/>
-      <c r="AF36" s="16"/>
-    </row>
-    <row r="37" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
         <v>33</v>
       </c>
@@ -6964,29 +6822,25 @@
       <c r="I37" s="14"/>
       <c r="J37" s="3"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
+      <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="14"/>
-      <c r="S37" s="3"/>
+      <c r="S37" s="14"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="14"/>
+      <c r="U37" s="3"/>
       <c r="V37" s="14"/>
-      <c r="W37" s="3"/>
+      <c r="W37" s="14"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
-      <c r="AC37" s="3"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="3"/>
-      <c r="AF37" s="3"/>
-    </row>
-    <row r="38" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="15">
         <v>34</v>
       </c>
@@ -7000,29 +6854,25 @@
       <c r="I38" s="15"/>
       <c r="J38" s="16"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
+      <c r="L38" s="16"/>
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
       <c r="P38" s="16"/>
       <c r="Q38" s="16"/>
       <c r="R38" s="15"/>
-      <c r="S38" s="16"/>
+      <c r="S38" s="15"/>
       <c r="T38" s="16"/>
-      <c r="U38" s="15"/>
+      <c r="U38" s="16"/>
       <c r="V38" s="15"/>
-      <c r="W38" s="16"/>
+      <c r="W38" s="15"/>
       <c r="X38" s="16"/>
       <c r="Y38" s="16"/>
       <c r="Z38" s="15"/>
-      <c r="AA38" s="15"/>
+      <c r="AA38" s="16"/>
       <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
-      <c r="AD38" s="15"/>
-      <c r="AE38" s="16"/>
-      <c r="AF38" s="16"/>
-    </row>
-    <row r="39" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
         <v>35</v>
       </c>
@@ -7036,29 +6886,25 @@
       <c r="I39" s="14"/>
       <c r="J39" s="3"/>
       <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
+      <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="14"/>
-      <c r="S39" s="3"/>
+      <c r="S39" s="14"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="14"/>
+      <c r="U39" s="3"/>
       <c r="V39" s="14"/>
-      <c r="W39" s="3"/>
+      <c r="W39" s="14"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="14"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15">
         <v>36</v>
       </c>
@@ -7072,29 +6918,25 @@
       <c r="I40" s="15"/>
       <c r="J40" s="16"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
+      <c r="L40" s="16"/>
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
       <c r="O40" s="16"/>
       <c r="P40" s="16"/>
       <c r="Q40" s="16"/>
       <c r="R40" s="15"/>
-      <c r="S40" s="16"/>
+      <c r="S40" s="15"/>
       <c r="T40" s="16"/>
-      <c r="U40" s="15"/>
+      <c r="U40" s="16"/>
       <c r="V40" s="15"/>
-      <c r="W40" s="16"/>
+      <c r="W40" s="15"/>
       <c r="X40" s="16"/>
       <c r="Y40" s="16"/>
       <c r="Z40" s="15"/>
-      <c r="AA40" s="15"/>
+      <c r="AA40" s="16"/>
       <c r="AB40" s="16"/>
-      <c r="AC40" s="16"/>
-      <c r="AD40" s="15"/>
-      <c r="AE40" s="16"/>
-      <c r="AF40" s="16"/>
-    </row>
-    <row r="41" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
         <v>37</v>
       </c>
@@ -7108,29 +6950,25 @@
       <c r="I41" s="14"/>
       <c r="J41" s="3"/>
       <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="14"/>
-      <c r="S41" s="3"/>
+      <c r="S41" s="14"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="14"/>
+      <c r="U41" s="3"/>
       <c r="V41" s="14"/>
-      <c r="W41" s="3"/>
+      <c r="W41" s="14"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
-      <c r="AD41" s="14"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="3"/>
-    </row>
-    <row r="42" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15">
         <v>38</v>
       </c>
@@ -7144,29 +6982,25 @@
       <c r="I42" s="15"/>
       <c r="J42" s="16"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
+      <c r="L42" s="16"/>
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
       <c r="O42" s="16"/>
       <c r="P42" s="16"/>
       <c r="Q42" s="16"/>
       <c r="R42" s="15"/>
-      <c r="S42" s="16"/>
+      <c r="S42" s="15"/>
       <c r="T42" s="16"/>
-      <c r="U42" s="15"/>
+      <c r="U42" s="16"/>
       <c r="V42" s="15"/>
-      <c r="W42" s="16"/>
+      <c r="W42" s="15"/>
       <c r="X42" s="16"/>
       <c r="Y42" s="16"/>
       <c r="Z42" s="15"/>
-      <c r="AA42" s="15"/>
+      <c r="AA42" s="16"/>
       <c r="AB42" s="16"/>
-      <c r="AC42" s="16"/>
-      <c r="AD42" s="15"/>
-      <c r="AE42" s="16"/>
-      <c r="AF42" s="16"/>
-    </row>
-    <row r="43" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
         <v>39</v>
       </c>
@@ -7180,29 +7014,25 @@
       <c r="I43" s="14"/>
       <c r="J43" s="3"/>
       <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
+      <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="14"/>
-      <c r="S43" s="3"/>
+      <c r="S43" s="14"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="14"/>
+      <c r="U43" s="3"/>
       <c r="V43" s="14"/>
-      <c r="W43" s="3"/>
+      <c r="W43" s="14"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
-      <c r="AD43" s="14"/>
-      <c r="AE43" s="3"/>
-      <c r="AF43" s="3"/>
-    </row>
-    <row r="44" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15">
         <v>40</v>
       </c>
@@ -7216,29 +7046,25 @@
       <c r="I44" s="15"/>
       <c r="J44" s="16"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
+      <c r="L44" s="16"/>
       <c r="M44" s="16"/>
       <c r="N44" s="16"/>
       <c r="O44" s="16"/>
       <c r="P44" s="16"/>
       <c r="Q44" s="16"/>
       <c r="R44" s="15"/>
-      <c r="S44" s="16"/>
+      <c r="S44" s="15"/>
       <c r="T44" s="16"/>
-      <c r="U44" s="15"/>
+      <c r="U44" s="16"/>
       <c r="V44" s="15"/>
-      <c r="W44" s="16"/>
+      <c r="W44" s="15"/>
       <c r="X44" s="16"/>
       <c r="Y44" s="16"/>
       <c r="Z44" s="15"/>
-      <c r="AA44" s="15"/>
+      <c r="AA44" s="16"/>
       <c r="AB44" s="16"/>
-      <c r="AC44" s="16"/>
-      <c r="AD44" s="15"/>
-      <c r="AE44" s="16"/>
-      <c r="AF44" s="16"/>
-    </row>
-    <row r="45" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
         <v>41</v>
       </c>
@@ -7252,29 +7078,25 @@
       <c r="I45" s="14"/>
       <c r="J45" s="3"/>
       <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="14"/>
-      <c r="S45" s="3"/>
+      <c r="S45" s="14"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="14"/>
+      <c r="U45" s="3"/>
       <c r="V45" s="14"/>
-      <c r="W45" s="3"/>
+      <c r="W45" s="14"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="14"/>
-      <c r="AA45" s="14"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
-      <c r="AC45" s="3"/>
-      <c r="AD45" s="14"/>
-      <c r="AE45" s="3"/>
-      <c r="AF45" s="3"/>
-    </row>
-    <row r="46" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="15">
         <v>42</v>
       </c>
@@ -7288,29 +7110,25 @@
       <c r="I46" s="15"/>
       <c r="J46" s="16"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
+      <c r="L46" s="16"/>
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
       <c r="O46" s="16"/>
       <c r="P46" s="16"/>
       <c r="Q46" s="16"/>
       <c r="R46" s="15"/>
-      <c r="S46" s="16"/>
+      <c r="S46" s="15"/>
       <c r="T46" s="16"/>
-      <c r="U46" s="15"/>
+      <c r="U46" s="16"/>
       <c r="V46" s="15"/>
-      <c r="W46" s="16"/>
+      <c r="W46" s="15"/>
       <c r="X46" s="16"/>
       <c r="Y46" s="16"/>
       <c r="Z46" s="15"/>
-      <c r="AA46" s="15"/>
+      <c r="AA46" s="16"/>
       <c r="AB46" s="16"/>
-      <c r="AC46" s="16"/>
-      <c r="AD46" s="15"/>
-      <c r="AE46" s="16"/>
-      <c r="AF46" s="16"/>
-    </row>
-    <row r="47" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14">
         <v>43</v>
       </c>
@@ -7324,29 +7142,25 @@
       <c r="I47" s="14"/>
       <c r="J47" s="3"/>
       <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="14"/>
-      <c r="S47" s="3"/>
+      <c r="S47" s="14"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="14"/>
+      <c r="U47" s="3"/>
       <c r="V47" s="14"/>
-      <c r="W47" s="3"/>
+      <c r="W47" s="14"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="14"/>
-      <c r="AA47" s="14"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="14"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-    </row>
-    <row r="48" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15">
         <v>44</v>
       </c>
@@ -7360,29 +7174,25 @@
       <c r="I48" s="15"/>
       <c r="J48" s="16"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
+      <c r="L48" s="16"/>
       <c r="M48" s="16"/>
       <c r="N48" s="16"/>
       <c r="O48" s="16"/>
       <c r="P48" s="16"/>
       <c r="Q48" s="16"/>
       <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
+      <c r="S48" s="15"/>
       <c r="T48" s="16"/>
-      <c r="U48" s="15"/>
+      <c r="U48" s="16"/>
       <c r="V48" s="15"/>
-      <c r="W48" s="16"/>
+      <c r="W48" s="15"/>
       <c r="X48" s="16"/>
       <c r="Y48" s="16"/>
       <c r="Z48" s="15"/>
-      <c r="AA48" s="15"/>
+      <c r="AA48" s="16"/>
       <c r="AB48" s="16"/>
-      <c r="AC48" s="16"/>
-      <c r="AD48" s="15"/>
-      <c r="AE48" s="16"/>
-      <c r="AF48" s="16"/>
-    </row>
-    <row r="49" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14">
         <v>45</v>
       </c>
@@ -7396,29 +7206,25 @@
       <c r="I49" s="14"/>
       <c r="J49" s="3"/>
       <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
+      <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="14"/>
-      <c r="S49" s="3"/>
+      <c r="S49" s="14"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="14"/>
+      <c r="U49" s="3"/>
       <c r="V49" s="14"/>
-      <c r="W49" s="3"/>
+      <c r="W49" s="14"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="14"/>
-      <c r="AA49" s="14"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
-      <c r="AC49" s="3"/>
-      <c r="AD49" s="14"/>
-      <c r="AE49" s="3"/>
-      <c r="AF49" s="3"/>
-    </row>
-    <row r="50" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15">
         <v>46</v>
       </c>
@@ -7432,29 +7238,25 @@
       <c r="I50" s="15"/>
       <c r="J50" s="16"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
+      <c r="L50" s="16"/>
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
       <c r="O50" s="16"/>
       <c r="P50" s="16"/>
       <c r="Q50" s="16"/>
       <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
+      <c r="S50" s="15"/>
       <c r="T50" s="16"/>
-      <c r="U50" s="15"/>
+      <c r="U50" s="16"/>
       <c r="V50" s="15"/>
-      <c r="W50" s="16"/>
+      <c r="W50" s="15"/>
       <c r="X50" s="16"/>
       <c r="Y50" s="16"/>
       <c r="Z50" s="15"/>
-      <c r="AA50" s="15"/>
+      <c r="AA50" s="16"/>
       <c r="AB50" s="16"/>
-      <c r="AC50" s="16"/>
-      <c r="AD50" s="15"/>
-      <c r="AE50" s="16"/>
-      <c r="AF50" s="16"/>
-    </row>
-    <row r="51" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14">
         <v>47</v>
       </c>
@@ -7468,29 +7270,25 @@
       <c r="I51" s="14"/>
       <c r="J51" s="3"/>
       <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
+      <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="14"/>
-      <c r="S51" s="3"/>
+      <c r="S51" s="14"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="14"/>
+      <c r="U51" s="3"/>
       <c r="V51" s="14"/>
-      <c r="W51" s="3"/>
+      <c r="W51" s="14"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="14"/>
-      <c r="AA51" s="14"/>
+      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
-      <c r="AC51" s="3"/>
-      <c r="AD51" s="14"/>
-      <c r="AE51" s="3"/>
-      <c r="AF51" s="3"/>
-    </row>
-    <row r="52" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15">
         <v>48</v>
       </c>
@@ -7504,29 +7302,25 @@
       <c r="I52" s="15"/>
       <c r="J52" s="16"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
+      <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
       <c r="O52" s="16"/>
       <c r="P52" s="16"/>
       <c r="Q52" s="16"/>
       <c r="R52" s="15"/>
-      <c r="S52" s="16"/>
+      <c r="S52" s="15"/>
       <c r="T52" s="16"/>
-      <c r="U52" s="15"/>
+      <c r="U52" s="16"/>
       <c r="V52" s="15"/>
-      <c r="W52" s="16"/>
+      <c r="W52" s="15"/>
       <c r="X52" s="16"/>
       <c r="Y52" s="16"/>
       <c r="Z52" s="15"/>
-      <c r="AA52" s="15"/>
+      <c r="AA52" s="16"/>
       <c r="AB52" s="16"/>
-      <c r="AC52" s="16"/>
-      <c r="AD52" s="15"/>
-      <c r="AE52" s="16"/>
-      <c r="AF52" s="16"/>
-    </row>
-    <row r="53" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14">
         <v>49</v>
       </c>
@@ -7540,29 +7334,25 @@
       <c r="I53" s="14"/>
       <c r="J53" s="3"/>
       <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
+      <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="14"/>
-      <c r="S53" s="3"/>
+      <c r="S53" s="14"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="14"/>
+      <c r="U53" s="3"/>
       <c r="V53" s="14"/>
-      <c r="W53" s="3"/>
+      <c r="W53" s="14"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="14"/>
-      <c r="AA53" s="14"/>
+      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
-      <c r="AC53" s="3"/>
-      <c r="AD53" s="14"/>
-      <c r="AE53" s="3"/>
-      <c r="AF53" s="3"/>
-    </row>
-    <row r="54" spans="1:32" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:28" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15">
         <v>50</v>
       </c>
@@ -7576,74 +7366,58 @@
       <c r="I54" s="15"/>
       <c r="J54" s="16"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
+      <c r="L54" s="16"/>
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
       <c r="O54" s="16"/>
       <c r="P54" s="16"/>
       <c r="Q54" s="16"/>
       <c r="R54" s="15"/>
-      <c r="S54" s="16"/>
+      <c r="S54" s="15"/>
       <c r="T54" s="16"/>
-      <c r="U54" s="15"/>
+      <c r="U54" s="16"/>
       <c r="V54" s="15"/>
-      <c r="W54" s="16"/>
+      <c r="W54" s="15"/>
       <c r="X54" s="16"/>
       <c r="Y54" s="16"/>
       <c r="Z54" s="15"/>
-      <c r="AA54" s="15"/>
+      <c r="AA54" s="16"/>
       <c r="AB54" s="16"/>
-      <c r="AC54" s="16"/>
-      <c r="AD54" s="15"/>
-      <c r="AE54" s="16"/>
-      <c r="AF54" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AF54" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A4:AB54" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="AF5:AF1000" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="AB5:AB1000" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Đang hoạt động,Hư hỏng / Chờ thanh lý,Đang lưu kho / Dự phòng"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Loại máy" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000001000000}">
-          <x14:formula1>
-            <xm:f>Data_Hidden!$A$3:$A$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>O5:O54</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Hệ điều hành" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000002000000}">
           <x14:formula1>
             <xm:f>Data_Hidden!$E$3:$E$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W5:W54</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Office" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000003000000}">
-          <x14:formula1>
-            <xm:f>Data_Hidden!$F$3:$F$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>X5:X54</xm:sqref>
+          <xm:sqref>T5:T54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Antivirus" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000004000000}">
           <x14:formula1>
             <xm:f>Data_Hidden!$G$3:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>Y5:Y54</xm:sqref>
+          <xm:sqref>U5:U54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Thời gian bảo hành (Còn/Hết)" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000005000000}">
           <x14:formula1>
             <xm:f>Data_Hidden!$K$3:$K$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AE5:AE54</xm:sqref>
+          <xm:sqref>AA5:AA54</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Lỗi nhập liệu" error="Dữ liệu không hợp lệ" promptTitle="Tình trạng" prompt="Vui lòng chọn trạng thái từ danh sách có sẵn" xr:uid="{00000000-0002-0000-0300-000006000000}">
           <x14:formula1>
             <xm:f>Data_Hidden!$H$3:$H$6</xm:f>
           </x14:formula1>
-          <xm:sqref>AF5:AF54</xm:sqref>
+          <xm:sqref>AB5:AB54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
